--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsThirdChannelRefExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsThirdChannelRefExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>我司物流商</t>
   </si>
@@ -58,6 +58,12 @@
     <t>默认手机号</t>
   </si>
   <si>
+    <t>店铺/平台</t>
+  </si>
+  <si>
+    <t>手机号码</t>
+  </si>
+  <si>
     <t>启用状态</t>
   </si>
   <si>
@@ -89,6 +95,12 @@
   </si>
   <si>
     <t>{.mobile}</t>
+  </si>
+  <si>
+    <t>{.platformShopName}</t>
+  </si>
+  <si>
+    <t>{.detailMobile}</t>
   </si>
   <si>
     <t>{.disabledName}</t>
@@ -109,7 +121,7 @@
     <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="177" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,6 +134,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.8"/>
+      <color rgb="FF871094"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -588,137 +606,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -735,6 +753,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1048,8 +1069,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.375" customWidth="1"/>
     <col min="2" max="2" width="15.25" customWidth="1"/>
@@ -1060,11 +1081,11 @@
     <col min="7" max="7" width="10.5" customWidth="1"/>
     <col min="8" max="8" width="12" style="1" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="11.5" customWidth="1"/>
-    <col min="11" max="11" width="19.625" customWidth="1"/>
+    <col min="10" max="12" width="11.5" customWidth="1"/>
+    <col min="13" max="13" width="19.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1098,41 +1119,56 @@
       <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>21</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="9:9">
+      <c r="I9" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsThirdChannelRefExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsThirdChannelRefExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>我司物流商</t>
   </si>
@@ -70,6 +70,9 @@
     <t>创建人</t>
   </si>
   <si>
+    <t>创建时间</t>
+  </si>
+  <si>
     <t>{.logisticsSupplierName}</t>
   </si>
   <si>
@@ -107,6 +110,9 @@
   </si>
   <si>
     <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.createTime}</t>
   </si>
 </sst>
 </file>
@@ -1069,7 +1075,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.375" customWidth="1"/>
@@ -1082,10 +1088,10 @@
     <col min="8" max="8" width="12" style="1" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
     <col min="10" max="12" width="11.5" customWidth="1"/>
-    <col min="13" max="13" width="19.625" customWidth="1"/>
+    <col min="13" max="14" width="19.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1125,46 +1131,52 @@
       <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="9:9">

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsThirdChannelRefExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsThirdChannelRefExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>我司物流商</t>
   </si>
@@ -55,9 +55,6 @@
     <t>推送类型</t>
   </si>
   <si>
-    <t>默认手机号</t>
-  </si>
-  <si>
     <t>店铺/平台</t>
   </si>
   <si>
@@ -97,13 +94,10 @@
     <t>{.pushTypeName}</t>
   </si>
   <si>
+    <t>{.platformShopName}</t>
+  </si>
+  <si>
     <t>{.mobile}</t>
-  </si>
-  <si>
-    <t>{.platformShopName}</t>
-  </si>
-  <si>
-    <t>{.detailMobile}</t>
   </si>
   <si>
     <t>{.disabledName}</t>
@@ -127,7 +121,7 @@
     <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="177" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,12 +134,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.8"/>
-      <color rgb="FF871094"/>
-      <name val="Courier New"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -612,137 +600,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -759,9 +747,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1075,8 +1060,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15.375" customWidth="1"/>
     <col min="2" max="2" width="15.25" customWidth="1"/>
@@ -1086,12 +1071,11 @@
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="10.5" customWidth="1"/>
     <col min="8" max="8" width="12" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="12" width="11.5" customWidth="1"/>
-    <col min="13" max="14" width="19.625" customWidth="1"/>
+    <col min="9" max="11" width="11.5" customWidth="1"/>
+    <col min="12" max="13" width="19.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1131,56 +1115,47 @@
       <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="9:9">
-      <c r="I9" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsThirdChannelRefExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsThirdChannelRefExport.xlsx
@@ -40,13 +40,13 @@
     <t>查询服务商</t>
   </si>
   <si>
-    <t>查询物流商</t>
-  </si>
-  <si>
-    <t>物流商编码</t>
-  </si>
-  <si>
-    <t>查询渠道名称</t>
+    <t>查询物流商（中文）</t>
+  </si>
+  <si>
+    <t>物流商编码（英文）</t>
+  </si>
+  <si>
+    <t>查询code</t>
   </si>
   <si>
     <t>是否推送电话</t>
@@ -740,10 +740,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -1100,19 +1100,19 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H2" s="1" t="s">
